--- a/Examples/test/test0.xlsx
+++ b/Examples/test/test0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctorr\Documents\Proyectos\TaesLab\Examples\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1B203C-ED4B-4213-ACF2-65A571EFA9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B71FAD-A352-44B0-A9A7-194560896600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
   <si>
     <t>key</t>
   </si>
@@ -240,6 +240,21 @@
   </si>
   <si>
     <t>F4+F7</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>F7+F8</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Singular</t>
   </si>
 </sst>
 </file>
@@ -759,7 +774,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja3"/>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -828,6 +843,14 @@
       </c>
       <c r="B8" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -840,7 +863,7 @@
           <x14:formula1>
             <xm:f>Validate!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B8</xm:sqref>
+          <xm:sqref>B2:B9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -943,7 +966,7 @@
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -966,21 +989,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Hoja5"/>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>Flows!A2</f>
         <v>F1</v>
@@ -988,8 +1020,17 @@
       <c r="B2">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2">
+        <v>110</v>
+      </c>
+      <c r="D2">
+        <v>110</v>
+      </c>
+      <c r="E2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>Flows!A3</f>
         <v>F2</v>
@@ -997,8 +1038,17 @@
       <c r="B3">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>Flows!A4</f>
         <v>F3</v>
@@ -1006,8 +1056,17 @@
       <c r="B4">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>Flows!A5</f>
         <v>F4</v>
@@ -1015,8 +1074,17 @@
       <c r="B5">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>40</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>Flows!A6</f>
         <v>F5</v>
@@ -1024,8 +1092,17 @@
       <c r="B6">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>Flows!A7</f>
         <v>F6</v>
@@ -1033,14 +1110,49 @@
       <c r="B7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>Flows!A8</f>
         <v>F7</v>
       </c>
       <c r="B8">
         <v>10</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>0.1</v>
+      </c>
+      <c r="D9">
+        <v>1E-3</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
